--- a/data/workshop/intervention-ranking.xlsx
+++ b/data/workshop/intervention-ranking.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://birminghamcitycouncil-my.sharepoint.com/personal/david_ellis_birmingham_gov_uk/Documents/Documents/Documents/MPH/Measles Modelling/Measles-System-Dynamics-BSol/data/workshop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{00F78CD3-76C1-4F19-B694-EA1AC4BC0A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C717DCC-4A42-45D2-8A6C-938B16B7C68B}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{00F78CD3-76C1-4F19-B694-EA1AC4BC0A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6446EF1-4903-4013-8294-2019BA4ED73F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{059ED7B8-75E7-42A8-944B-E691196377F3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="rank-points" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Intervention</t>
   </si>
@@ -75,6 +76,12 @@
   </si>
   <si>
     <t>Train voluntary and community sector organisations to have difficult conversations (LA/NHS)</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Points</t>
   </si>
 </sst>
 </file>
@@ -635,4 +642,70 @@
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 OFFICIAL</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B396F8-02FE-4DF8-BD4C-882BFC899EAC}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>